--- a/artfynd/A 35509-2026 artfynd.xlsx
+++ b/artfynd/A 35509-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194054</v>
       </c>
       <c r="B2" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35509-2026 artfynd.xlsx
+++ b/artfynd/A 35509-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194054</v>
       </c>
       <c r="B2" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35509-2026 artfynd.xlsx
+++ b/artfynd/A 35509-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194054</v>
       </c>
       <c r="B2" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35509-2026 artfynd.xlsx
+++ b/artfynd/A 35509-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194054</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
